--- a/compare_infer.xlsx
+++ b/compare_infer.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +28,23 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
+        <bgColor rgb="00FFD966"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,10 +65,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -427,39 +443,50 @@
   </sheetPr>
   <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>sft_info</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>sft_text</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>sft_output</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>grpo_text</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>grpo_output</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了593分，能否报考物联网工程专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+    <row r="2" ht="135" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>{'detail': {'专业': '物联网工程', '平均分': 503, '序号': 29, '录取数': 51, '最低位次号': 172871, '最低分': 496, '最高分': 529, '省控线': 492, '计划数': 51}, 'score': 593, 'rank': None}</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了593分，能否报考物联网工程专业？</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -467,15 +494,7 @@
 Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了593分，能否报考物联网工程专业？&lt;REASONING&gt;好的，针对我考了593分，能否报考物联网工程专业？的问题，可以搜索到如下相关信息浙江省2024年本科物联网工程录取情况如下浙江省2024年本科物联网工程专业的省控线为492分。最高分为529分，最低分为496分，平均分为503分，最低位次号为172871。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了593分，能够报考物联网工程专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了593分，能否报考物联网工程专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -484,16 +503,21 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了506分，能否报考家政学专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+    <row r="3" ht="135" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>{'detail': {'专业': '家政学', '平均分': 555, '序号': 24, '录取数': 13, '最低位次号': 109812, '最低分': 551, '最高分': 563, '省控线': 492, '计划数': 13}, 'score': 506, 'rank': None}</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了506分，能否报考家政学专业？</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -501,33 +525,30 @@
 Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了506分，能否报考家政学专业？&lt;REASONING&gt;好的，针对我考了506分，能否报考家政学专业？的问题，可以搜索到如下相关信息浙江省2024年本科家政学录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '家政学', '13人', '13人', '492分', '506分', '493分', '498分', '163422']&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了506分，可以报考家政学专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了506分，能否报考家政学专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了506分，能否报考家政学专业？&lt;REASONING&gt;好的，针对我考了506分，能否报考家政学专业？的问题，可以搜索到如下相关信息浙江省2024年本科家政学录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '家政学', '13人', '13人', '492分', '563分', '551分', '555分', '109812']&lt;/REASON&gt;&lt;SOLUTION&gt;我考了506分，不能报考家政学专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了456分，能否报考环境工程专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了506分，能否报考家政学专业？&lt;REASONING&gt;好的，针对我考了506分，能否报考家政学专业？的问题，可以搜索到如下相关信息浙江省2024年本科家政学录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '家政学录取情况', '13人', '13人', '492分', '563分', '551分', '555分', '109812']&lt;/REASON&gt;&lt;SOLUTION&gt;我考了506分，不能报考家政学专业&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="135" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>{'detail': {'专业': '环境工程', '平均分': 485, '序号': 31, '录取数': 100, '最低位次号': 193639, '最低分': 477, '最高分': 519, '省控线': 492, '计划数': 100}, 'score': 456, 'rank': None}</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了456分，能否报考环境工程专业？</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -535,15 +556,7 @@
 Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了456分，能否报考环境工程专业？&lt;REASONING&gt;好的，针对我考了456分，能否报考环境工程专业？的问题，可以搜索到如下相关信息浙江省2024年本科环境工程录取情况如下浙江省2024年本科环境工程专业的最低分是519分，最高分是529分，平均分是531分，最低位次号为167417。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了456分，不能报考环境工程专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了456分，能否报考环境工程专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -552,16 +565,21 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了553分，能否报考城乡规划专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+    <row r="5" ht="135" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>{'detail': {'专业': '城乡规划', '平均分': 549, '序号': 6, '录取数': 60, '最低位次号': 116183, '最低分': 546, '最高分': 559, '省控线': 492, '计划数': 60}, 'score': 553, 'rank': None}</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了553分，能否报考城乡规划专业？</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -569,49 +587,38 @@
 Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了553分，能否报考城乡规划专业？&lt;REASONING&gt;好的，针对我考了553分，能否报考城乡规划专业？的问题，可以搜索到如下相关信息浙江省2024年本科城乡规划录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['161', '城乡规划', '60人', '60人', '492分', '559分', '546分', '549分', '116183']&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了553分，可以报考城乡规划专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了553分，能否报考城乡规划专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了553分，能否报考城乡规划专业？&lt;REASONING&gt;好的，针对我考了553分，能否报考城乡规划专业？的问题，可以搜索到如下相关信息浙江省2024年本科城乡规划录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '城乡规划录取情况', '60人', '60人', '492分', '559分', '546分', '549分', '116183']\n['2', '城乡规划录取情况', '60人', '60人', '492分', '559分', '546分', '549分', '116183']\n['3', '城乡规划录取情况', '60人', '60人', '492分', '559分', '546分', '549分', '116183']\n['4', '城乡规划录取情况', '60人', '60人', '492分', '559分', '546分', '549分', '116183']\n['5', '城乡规划录取情况', '60人', '60人', '492分', '559分', '546分', '549分', '116183']\n['6', '城乡规划录取情况', '60人', '60人', '492分', '559分', '546分', '549分', '116183']\n['7', '城乡规划录取情况', '60人', '60人', '492分', '559分', '546分', '549分', '116183']\n['8', '城乡规划录取情况', '60人', '60人', '492分', '559分', '546分', '549分', '116183']\n['9', '城乡规划录取情况', '</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了505分，能否报考公共事业管理专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了505分，能否报考公共事业管理专业？&lt;REASONING&gt;好的，针对我考了505分，能否报考公共事业管理专业？的问题，可以搜索到如下相关信息浙江省2024年本科公共事业管理录取情况如下浙江省2024年本科公共事业管理专业的录取数为20人，省控线为492分。最高分为569分，最低分为549分，平均分为551分，最低位次号为112613。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了505分，可以报考公共事业管理专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了505分，能否报考公共事业管理专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了553分，能否报考城乡规划专业？&lt;REASONING&gt;好的，针对我考了553分，能否报考城乡规划专业？的问题，可以搜索到如下相关信息浙江省2024年本科城乡规划录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '城乡规划录取情况', '60', '60', '492', '569', '551', '555', '112613']&lt;/REASON&gt;&lt;SOLUTION&gt;我考了553分，可以报考城乡规划专业&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="135" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>{'detail': {'专业': '公共事业管理', '平均分': 551, '序号': 5, '录取数': 20, '最低位次号': 112613, '最低分': 549, '最高分': 569, '省控线': 492, '计划数': 20}, 'score': 505, 'rank': None}</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了505分，能否报考公共事业管理专业？</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了505分，能否报考公共事业管理专业？&lt;REASONING&gt;好的，针对我考了505分，能否报考公共事业管理专业？的问题，可以搜索到如下相关信息浙江省2024年本科公共事业管理录取情况如下浙江省2024年本科公共事业管理专业的录取数为20人，省控线为492分。最高分为569分，最低分为549分，平均分为551分，最低位次号为112613。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了505分，能够报考公共事业管理专业&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -620,16 +627,21 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了457分，能否报考人工智能专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+    <row r="7" ht="135" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>{'detail': {'专业': '人工智能', '平均分': 503, '序号': 26, '录取数': 99, '最低位次号': 173398, '最低分': 496, '最高分': 524, '省控线': 492, '计划数': 99}, 'score': 457, 'rank': None}</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了457分，能否报考人工智能专业？</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -637,33 +649,30 @@
 Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了457分，能否报考人工智能专业？&lt;REASONING&gt;好的，针对我考了457分，能否报考人工智能专业？的问题，可以搜索到如下相关信息浙江省2024年本科人工智能录取情况如下浙江省2024年本科人工智能专业的录取计划数为99人，录取数为99人，省控线为492分。最高分为524分，最低分为496分，平均分为503分，最低位次号为173398。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了457分，能够报考人工智能专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了457分，能否报考人工智能专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了457分，能否报考人工智能专业？&lt;REASONING&gt;好的，针对我考了457分，能否报考人工智能专业？的问题，可以搜索到如下相关信息浙江省2024年本科人工智能录取情况如下浙江省2024年本科人工智能专业的录取计划数为99人，录取数为99人，省控线为492分。最高分为524分，最低分为496分，平均分为503分，最低位次号为173398。&lt;/REASON&gt;&lt;SOLUTION&gt;我考了457分，不能报考人工智能专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了484分，能否报考医学检验技术专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了457分，能否报考人工智能专业？&lt;REASONING&gt;好的，针对我考了457分，能否报考人工智能专业？的问题，可以搜索到如下相关信息浙江省2024年本科人工智能录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '人工智能', '99', '99', '492', '524', '496', '503', '173398']&lt;/REASON&gt;&lt;SOLUTION&gt;我考了457分，可以报考人工智能专业&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="135" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>{'detail': {'专业': '医学检验技术', '平均分': 506, '序号': 39, '录取数': 43, '最低位次号': 183515, '最低分': 486, '最高分': 541, '省控线': 492, '计划数': 43}, 'score': 484, 'rank': None}</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了484分，能否报考医学检验技术专业？</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -671,49 +680,38 @@
 Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了484分，能否报考医学检验技术专业？&lt;REASONING&gt;好的，针对我考了484分，能否报考医学检验技术专业？的问题，可以搜索到如下相关信息浙江省2024年本科医学检验技术录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '医学检验技术', '43人', '43人', '492分', '541分', '486分', '506分', '183515']&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了484分，可以报考医学检验技术专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了484分，能否报考医学检验技术专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了484分，能否报考医学检验技术专业？&lt;REASONING&gt;好的，针对我考了484分，能否报考医学检验技术专业？的问题，可以搜索到如下相关信息浙江省2024年本科医学检验技术录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '医学检验技术', '43人', '43人', '492分', '541分', '486分', '506分', '183515']&lt;/REASON&gt;&lt;SOLUTION&gt;我考了484分，可以报考医学检验技术专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了600分，能否报考建筑学专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了600分，能否报考建筑学专业？&lt;REASONING&gt;好的，针对我考了600分，能否报考建筑学专业？的问题，可以搜索到如下相关信息浙江省2024年本科建筑学录取情况如下录取数省控线录取数省控线最高分最低分平均分最低位次号13人492分576分585分193639&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了600分，能够报考建筑学专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了600分，能否报考建筑学专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了484分，能否报考医学检验技术专业？&lt;REASONING&gt;好的，针对我考了484分，能否报考医学检验技术专业？的问题，可以搜索到如下相关信息浙江省2024年本科医学检验技术录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '医学检验技术', '43人', '43人', '492分', '541分', '486分', '506分', '183515']\n&lt;/REASON&gt;&lt;SOLUTION&gt;我考了484分，可以报考医学检验技术专业&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>{'detail': {'专业': '建筑学', '平均分': 546, '序号': 8, '录取数': 54, '最低位次号': 120613, '最低分': 542, '最高分': 572, '省控线': 492, '计划数': 54}, 'score': 600, 'rank': None}</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我考了600分，能否报考建筑学专业？</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了600分，能否报考建筑学专业？&lt;REASONING&gt;好的，针对我考了600分，能否报考建筑学专业？的问题，可以搜索到如下相关信息浙江省2024年本科建筑学录取情况如下浙江省2024年本科建筑学专业的省控线为492分。最高分为572分，最低分为542分，平均分为546分，最低位次号为120613。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了600分，能够报考建筑学专业&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -722,50 +720,52 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为134879，能否报考物联网工程专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为134879，能否报考物联网工程专业？&lt;REASONING&gt;好的，针对我的位次为134879，能否报考物联网工程专业？的问题，可以搜索到如下相关信息浙江省2024年本科物联网工程录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['121311', '物联网工程', '51', '51', '492', '529', '496', '503', '168841']&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为134879，可以报考物联网工程专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为134879，能否报考物联网工程专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为134879，能否报考物联网工程专业？&lt;REASONING&gt;好的，针对我的位次为134879，能否报考物联网工程专业？的问题，可以搜索到如下相关信息浙江省2024年本科物联网工程录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '物联网工程', '51', '51', '492', '529', '496', '503', '162881']&lt;/REASON&gt;&lt;SOLUTION&gt;我的位次为134879，可以报考物联网工程专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为139298，能否报考家政学专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+    <row r="10" ht="135" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>{'detail': {'专业': '物联网工程', '平均分': 503, '序号': 29, '录取数': 51, '最低位次号': 172871, '最低分': 496, '最高分': 529, '省控线': 492, '计划数': 51}, 'score': None, 'rank': 134879}</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为134879，能否报考物联网工程专业？</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为134879，能否报考物联网工程专业？&lt;REASONING&gt;好的，针对我的位次为134879，能否报考物联网工程专业？的问题，可以搜索到如下相关信息浙江省2024年本科物联网工程录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['161214', '物联网工程', '51', '51', '492', '529', '496', '503', '172813']&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为134879，可以报考物联网工程专业&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为134879，能否报考物联网工程专业？&lt;REASONING&gt;好的，针对我的位次为134879，能否报考物联网工程专业？的问题，可以搜索到如下相关信息浙江省2024年本科物联网工程录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '物联网工程', '51', '51', '492', '529', '496', '503', '168841']&lt;/REASON&gt;&lt;SOLUTION&gt;我的位次为134879，可以报考物联网工程专业&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="135" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>{'detail': {'专业': '家政学', '平均分': 555, '序号': 24, '录取数': 13, '最低位次号': 109812, '最低分': 551, '最高分': 563, '省控线': 492, '计划数': 13}, 'score': None, 'rank': 139298}</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为139298，能否报考家政学专业？</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -773,15 +773,7 @@
 Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为139298，能否报考家政学专业？&lt;REASONING&gt;好的，针对我的位次为139298，能否报考家政学专业？的问题，可以搜索到如下相关信息浙江省2024年本科家政学录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['161312', '家政学', '13人', '13人', '492分', '563分', '551分', '555分', '109812']&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为139298，可以报考家政学专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为139298，能否报考家政学专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -790,16 +782,21 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为103570，能否报考环境工程专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="12" ht="135" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>{'detail': {'专业': '环境工程', '平均分': 485, '序号': 31, '录取数': 100, '最低位次号': 193639, '最低分': 477, '最高分': 519, '省控线': 492, '计划数': 100}, 'score': None, 'rank': 103570}</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为103570，能否报考环境工程专业？</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -807,15 +804,7 @@
 Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为103570，能否报考环境工程专业？&lt;REASONING&gt;好的，针对我的位次为103570，能否报考环境工程专业？的问题，可以搜索到如下相关信息浙江省2024年本科环境工程录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['103570', '环境工程', '100', '100', '492', '519', '477', '485', '193639']&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为103570，可以报考环境工程专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为103570，能否报考环境工程专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -824,16 +813,21 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为174322，能否报考城乡规划专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+    <row r="13" ht="135" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>{'detail': {'专业': '城乡规划', '平均分': 549, '序号': 6, '录取数': 60, '最低位次号': 116183, '最低分': 546, '最高分': 559, '省控线': 492, '计划数': 60}, 'score': None, 'rank': 174322}</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为174322，能否报考城乡规划专业？</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -841,15 +835,7 @@
 Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为174322，能否报考城乡规划专业？&lt;REASONING&gt;好的，针对我的位次为174322，能否报考城乡规划专业？的问题，可以搜索到如下相关信息浙江省2024年本科城乡规划录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['191', '城乡规划', '60', '60', '492', '559', '546', '549', '174322']&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为174322，可以报考城乡规划专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为174322，能否报考城乡规划专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -858,16 +844,21 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为176158，能否报考公共事业管理专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+    <row r="14" ht="150" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>{'detail': {'专业': '公共事业管理', '平均分': 551, '序号': 5, '录取数': 20, '最低位次号': 112613, '最低分': 549, '最高分': 569, '省控线': 492, '计划数': 20}, 'score': None, 'rank': 176158}</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为176158，能否报考公共事业管理专业？</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -875,15 +866,7 @@
 Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为176158，能否报考公共事业管理专业？&lt;REASONING&gt;好的，针对我的位次为176158，能否报考公共事业管理专业？的问题，可以搜索到如下相关信息浙江省2024年本科公共事业管理录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['193613', '公共事业管理', '20', '20', '492', '569', '549', '551', '176158']&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为176158，可以报考公共事业管理专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为176158，能否报考公共事业管理专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -892,16 +875,21 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为122789，能否报考人工智能专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>{'detail': {'专业': '人工智能', '平均分': 503, '序号': 26, '录取数': 99, '最低位次号': 173398, '最低分': 496, '最高分': 524, '省控线': 492, '计划数': 99}, 'score': None, 'rank': 122789}</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为122789，能否报考人工智能专业？</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -909,33 +897,30 @@
 Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为122789，能否报考人工智能专业？&lt;REASONING&gt;好的，针对我的位次为122789，能否报考人工智能专业？的问题，可以搜索到如下相关信息浙江省2024年本科人工智能录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['191227', '人工智能', '99人', '99人', '492分', '524分', '496分', '503分', '173398']&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为122789，可以报考人工智能专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为122789，能否报考人工智能专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为122789，能否报考人工智能专业？&lt;REASONING&gt;好的，针对我的位次为122789，能否报考人工智能专业？的问题，可以搜索到如下相关信息浙江省2024年本科人工智能录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['193', '人工智能', '99', '99', '492', '524', '496', '503', '173398']&lt;/REASON&gt;&lt;SOLUTION&gt;我的位次为122789，可以报考人工智能专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为126367，能否报考医学检验技术专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为122789，能否报考人工智能专业？&lt;REASONING&gt;好的，针对我的位次为122789，能否报考人工智能专业？的问题，可以搜索到如下相关信息浙江省2024年本科人工智能录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['191', '人工智能', '99', '99', '492', '524', '496', '503', '173398']&lt;/REASON&gt;&lt;SOLUTION&gt;我的位次为122789，可以报考人工智能专业&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>{'detail': {'专业': '医学检验技术', '平均分': 506, '序号': 39, '录取数': 43, '最低位次号': 183515, '最低分': 486, '最高分': 541, '省控线': 492, '计划数': 43}, 'score': None, 'rank': 126367}</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为126367，能否报考医学检验技术专业？</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -943,15 +928,7 @@
 Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为126367，能否报考医学检验技术专业？&lt;REASONING&gt;好的，针对我的位次为126367，能否报考医学检验技术专业？的问题，可以搜索到如下相关信息浙江省2024年本科医学检验技术录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '医学检验技术', '43人', '43人', '492分', '541分', '486分', '506分', '183515']&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为126367，可以报考医学检验技术专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为126367，能否报考医学检验技术专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -960,16 +937,21 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为187928，能否报考建筑学专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+    <row r="17" ht="135" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>{'detail': {'专业': '建筑学', '平均分': 546, '序号': 8, '录取数': 54, '最低位次号': 120613, '最低分': 542, '最高分': 572, '省控线': 492, '计划数': 54}, 'score': None, 'rank': 187928}</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为187928，能否报考建筑学专业？</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>You are given a problem.
 Think about the problem and provide your working out.
@@ -977,20 +959,12 @@
 Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为187928，能否报考建筑学专业？&lt;REASONING&gt;好的，针对我的位次为187928，能否报考建筑学专业？的问题，可以搜索到如下相关信息浙江省2024年本科建筑学录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '建筑学录取情况', '54人', '54人', '492分', '572分', '542分', '546分', '187928']&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为187928，可以报考建筑学专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;&lt;|endoftext|&gt;我的位次为187928，能否报考建筑学专业？&lt;REASONING&gt;</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>You are given a problem.
-Think about the problem and provide your working out.
-Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为187928，能否报考建筑学专业？&lt;REASONING&gt;好的，针对我的位次为187928，能否报考建筑学专业？的问题，可以搜索到如下相关信息浙江省2024年本科建筑学录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '建筑学录取情况', '54人', '54人', '492分', '572分', '542分', '546分', '187928']&lt;/REASON&gt;&lt;SOLUTION&gt;我的位次为187928，可以报考建筑学专业&lt;/SOLUTION&gt;</t>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>You are given a problem.
+Think about the problem and provide your working out.
+Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为187928，能否报考建筑学专业？&lt;REASONING&gt;好的，针对我的位次为187928，能否报考建筑学专业？的问题，可以搜索到如下相关信息浙江省2024年本科建筑学录取情况如下浙江省2024年本科建筑学专业的录取数为54人，省控线为492分。最高分为572分，最低分为542分，平均分为546分，最低位次号为120613。&lt;/REASON&gt;&lt;SOLUTION&gt;我的位次为187928，不能报考建筑学专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
     </row>

--- a/compare_infer.xlsx
+++ b/compare_infer.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="135" customHeight="1">
+    <row r="2" ht="165" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>{'detail': {'专业': '物联网工程', '平均分': 503, '序号': 29, '录取数': 51, '最低位次号': 172871, '最低分': 496, '最高分': 529, '省控线': 492, '计划数': 51}, 'score': 593, 'rank': None}</t>
@@ -491,7 +491,7 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了593分，能否报考物联网工程专业？&lt;REASONING&gt;好的，针对我考了593分，能否报考物联网工程专业？的问题，可以搜索到如下相关信息浙江省2024年本科物联网工程录取情况如下浙江省2024年本科物联网工程专业的省控线为492分。最高分为529分，最低分为496分，平均分为503分，最低位次号为172871。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了593分，能够报考物联网工程专业&lt;/SOLUTION&gt;</t>
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了593分，能否报考物联网工程专业？&lt;REASONING&gt;好的，针对我考了593分，能否报考物联网工程专业？的问题，可以搜索到如下相关信息浙江省2024年本科物联网工程录取情况如下浙江省2024年本科物联网工程专业的计划数为51人，录取数为51人，省控线为492分。最高分为529分，最低分为496分，平均分为503分，最低位次号为172871。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了593分，可以报考物联网工程专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -499,11 +499,11 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了593分，能否报考物联网工程专业？&lt;REASONING&gt;好的，针对我考了593分，能否报考物联网工程专业？的问题，可以搜索到如下相关信息浙江省2024年本科物联网工程录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '物联网工程', '51', '51', '492', '529', '496', '503', '172871']&lt;/REASON&gt;&lt;SOLUTION&gt;我考了593分，可以报考物联网工程专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="135" customHeight="1">
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了593分，能否报考物联网工程专业？&lt;REASONING&gt;好的，针对“我考了593分，能否报考物联网工程专业？”的问题，可以搜索到如下相关信息浙江省2024年本科物联网工程专业的录取计划数为51人，录取数为51人，省控线为492分。最高分为529分，最低分为496分，平均分为503分，最低位次号为172871。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了593分，高于省控线492分，低于最高分529分，对应的情况为大于或等于492且小于519分，小于529分，选择情况，因此可以报考物联网工程专业，对应的的情况为是大于或等于492且小于519分，小于529分，选择。因此，我考了593分，能够报考物联网工程专业，对应的的情况为是大于或等于492且小于519分，小于529分，选择。&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>{'detail': {'专业': '家政学', '平均分': 555, '序号': 24, '录取数': 13, '最低位次号': 109812, '最低分': 551, '最高分': 563, '省控线': 492, '计划数': 13}, 'score': 506, 'rank': None}</t>
@@ -530,11 +530,11 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了506分，能否报考家政学专业？&lt;REASONING&gt;好的，针对我考了506分，能否报考家政学专业？的问题，可以搜索到如下相关信息浙江省2024年本科家政学录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '家政学录取情况', '13人', '13人', '492分', '563分', '551分', '555分', '109812']&lt;/REASON&gt;&lt;SOLUTION&gt;我考了506分，不能报考家政学专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="135" customHeight="1">
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了506分，能否报考家政学专业？&lt;REASONING&gt;好的，针对“我考了506分，能否报考家政学专业？”的问题，可以搜索到如下相关信息浙江省2024年本科家政学专业的录取计划数为13人，录取数为13人，省控线为492分。最高分为563分，最低分为551分，平均分为555分，最低位次号为109812。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了506分，高于省控线492分，低于最高分555分，对应的情况为大于等于492且小于556分，小于559分，选择情况，因此不能报考家政学专业，对应的的情况为不可以报考家政学专业。因此，我不能报考家政学专业，对应的的情况为不可以报考家政学专业。&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>{'detail': {'专业': '环境工程', '平均分': 485, '序号': 31, '录取数': 100, '最低位次号': 193639, '最低分': 477, '最高分': 519, '省控线': 492, '计划数': 100}, 'score': 456, 'rank': None}</t>
@@ -553,7 +553,7 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了456分，能否报考环境工程专业？&lt;REASONING&gt;好的，针对我考了456分，能否报考环境工程专业？的问题，可以搜索到如下相关信息浙江省2024年本科环境工程录取情况如下浙江省2024年本科环境工程专业的最低分是519分，最高分是529分，平均分是531分，最低位次号为167417。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了456分，不能报考环境工程专业&lt;/SOLUTION&gt;</t>
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了456分，能否报考环境工程专业？&lt;REASONING&gt;好的，针对我考了456分，能否报考环境工程专业？的问题，可以搜索到如下相关信息浙江省2024年本科环境工程录取情况如下浙江省2024年本科环境工程专业的最低分是519分，最高分是529分，平均分是531分，最低位次号为161814。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了456分，不能报考环境工程专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -561,11 +561,11 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了456分，能否报考环境工程专业？&lt;REASONING&gt;好的，针对我考了456分，能否报考环境工程专业？的问题，可以搜索到如下相关信息浙江省2024年本科环境工程录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['123', '环境工程', '100', '100', '492', '519', '477', '485', '193639']&lt;/REASON&gt;&lt;SOLUTION&gt;我考了456分，不能报考环境工程专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="135" customHeight="1">
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了456分，能否报考环境工程专业？&lt;REASONING&gt;好的，针对“我考了456分，能否报考环境工程专业？”的问题，可以搜索到如下相关信息浙江省2024年本科环境工程专业的录取计划数为100人，录取数为100人，省控线为492分。最高分为519分，最低分为477分，平均分为485分，最低位次号为193639。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了456分，高于省控线492分，低于最高分519分，对应的情况为大于等于省控线且小于最高分，小于等于最低分，选择情况，因此不能报考环境工程专业，对应的的情况为不可以报考环境工程专业。因此，我不能报考环境工程专业，对应的的情况为不可以报考环境工程专业。&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="165" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>{'detail': {'专业': '城乡规划', '平均分': 549, '序号': 6, '录取数': 60, '最低位次号': 116183, '最低分': 546, '最高分': 559, '省控线': 492, '计划数': 60}, 'score': 553, 'rank': None}</t>
@@ -584,7 +584,7 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了553分，能否报考城乡规划专业？&lt;REASONING&gt;好的，针对我考了553分，能否报考城乡规划专业？的问题，可以搜索到如下相关信息浙江省2024年本科城乡规划录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['161', '城乡规划', '60人', '60人', '492分', '559分', '546分', '549分', '116183']&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了553分，可以报考城乡规划专业&lt;/SOLUTION&gt;</t>
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了553分，能否报考城乡规划专业？&lt;REASONING&gt;好的，针对我考了553分，能否报考城乡规划专业？的问题，可以搜索到如下相关信息浙江省2024年本科城乡规划录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '城乡规划', '60人', '60人', '492分', '559分', '546分', '549分', '116183']&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了553分，可以报考城乡规划专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -592,11 +592,11 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了553分，能否报考城乡规划专业？&lt;REASONING&gt;好的，针对我考了553分，能否报考城乡规划专业？的问题，可以搜索到如下相关信息浙江省2024年本科城乡规划录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '城乡规划录取情况', '60', '60', '492', '569', '551', '555', '112613']&lt;/REASON&gt;&lt;SOLUTION&gt;我考了553分，可以报考城乡规划专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="135" customHeight="1">
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了553分，能否报考城乡规划专业？&lt;REASONING&gt;好的，针对“我考了553分，能否报考城乡规划专业？”的问题，可以搜索到如下相关信息浙江省2024年本科城乡规划录取情况如下浙江省2024年本科城乡规划专业的录取计划数为60人，录取数为60人，省控线为492分。最高分为559分，最低分为546分，平均分为549分，最低位次号为116183。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了553分，高于省控线492分，低于最高分549分，对应的情况为大于或等于省控线且小于最高分，小于等于最低分，选择情况，因此可以报考城乡规划专业，对应的的情况为是大于或等于省控线且小于最高分，小于等于最低分，选择。因此，我考了553分，能够报考城乡规划专业，对应的的情况为是是大于或等于省控线且小于最高分，小于等于最低分，选择。&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>{'detail': {'专业': '公共事业管理', '平均分': 551, '序号': 5, '录取数': 20, '最低位次号': 112613, '最低分': 549, '最高分': 569, '省控线': 492, '计划数': 20}, 'score': 505, 'rank': None}</t>
@@ -623,11 +623,11 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了505分，能否报考公共事业管理专业？&lt;REASONING&gt;好的，针对我考了505分，能否报考公共事业管理专业？的问题，可以搜索到如下相关信息浙江省2024年本科公共事业管理录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '公共事业管理', '20', '20', '492', '569', '549', '551', '112613']&lt;/REASON&gt;&lt;SOLUTION&gt;我考了505分，可以报考公共事业管理专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="135" customHeight="1">
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了505分，能否报考公共事业管理专业？&lt;REASONING&gt;好的，针对“我考了505分，能否报考公共事业管理专业？”的问题，可以搜索到如下相关信息浙江省2024年本科公共事业管理专业的录取计划数为20人，录取数为20人，省控线为492分。最高分为569分，最低分为549分，平均分为551分，最低位次号为112613。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了505分，高于省控线492分，低于最高分553分，对应的情况为大于等于492且小于555分，小于559分，选择情况，因此不能报考公共事业管理专业，对应的的情况为不可以报考公共事业管理专业。因此，我不能报考公共事业管理专业，对应的的情况为不可以报考公共事业管理专业。&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="165" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>{'detail': {'专业': '人工智能', '平均分': 503, '序号': 26, '录取数': 99, '最低位次号': 173398, '最低分': 496, '最高分': 524, '省控线': 492, '计划数': 99}, 'score': 457, 'rank': None}</t>
@@ -646,7 +646,7 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了457分，能否报考人工智能专业？&lt;REASONING&gt;好的，针对我考了457分，能否报考人工智能专业？的问题，可以搜索到如下相关信息浙江省2024年本科人工智能录取情况如下浙江省2024年本科人工智能专业的录取计划数为99人，录取数为99人，省控线为492分。最高分为524分，最低分为496分，平均分为503分，最低位次号为173398。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了457分，能够报考人工智能专业&lt;/SOLUTION&gt;</t>
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了457分，能否报考人工智能专业？&lt;REASONING&gt;好的，针对我考了457分，能否报考人工智能专业？的问题，可以搜索到如下相关信息浙江省2024年本科人工智能录取情况如下浙江省2024年本科人工智能专业的录取计划数为99人，录取数为99人，省控线为492分。最高分为524分，最低分为496分，平均分为503分，最低位次号为173398。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了457分，不能报考人工智能专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -654,11 +654,11 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了457分，能否报考人工智能专业？&lt;REASONING&gt;好的，针对我考了457分，能否报考人工智能专业？的问题，可以搜索到如下相关信息浙江省2024年本科人工智能录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '人工智能', '99', '99', '492', '524', '496', '503', '173398']&lt;/REASON&gt;&lt;SOLUTION&gt;我考了457分，可以报考人工智能专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="135" customHeight="1">
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了457分，能否报考人工智能专业？&lt;REASONING&gt;好的，针对“我考了457分，能否报考人工智能专业？”的问题，可以搜索到如下相关信息浙江省2024年本科人工智能录取情况如下浙江省2024年本科人工智能专业的录取计划数为99人，录取数为99人，省控线为492分。最高分为524分，最低分为496分，平均分为503分，最低位次号为173398。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了457分，高于省控线492分，低于最高分524分，对应的情况为大于等于492且小于500分，小于512分，因此不能报考人工智能专业，对应的的情况为大于等于492且小于500分。因此，我不能报考人工智能专业，对应的的情况为不可以报考人工智能专业。因此，我考了457分，不能报考人工智能专业，对应的的情况为不可以报考人工智能专业。&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>{'detail': {'专业': '医学检验技术', '平均分': 506, '序号': 39, '录取数': 43, '最低位次号': 183515, '最低分': 486, '最高分': 541, '省控线': 492, '计划数': 43}, 'score': 484, 'rank': None}</t>
@@ -685,11 +685,11 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了484分，能否报考医学检验技术专业？&lt;REASONING&gt;好的，针对我考了484分，能否报考医学检验技术专业？的问题，可以搜索到如下相关信息浙江省2024年本科医学检验技术录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '医学检验技术', '43人', '43人', '492分', '541分', '486分', '506分', '183515']\n&lt;/REASON&gt;&lt;SOLUTION&gt;我考了484分，可以报考医学检验技术专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="120" customHeight="1">
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了484分，能否报考医学检验技术专业？&lt;REASONING&gt;好的，针对“我考了484分，能否报考医学检验技术专业？”的问题，可以搜索到如下相关信息浙江省2024年本科医学检验技术专业的录取计划数为43人，录取数为43人，省控线为492分。最高分为541分，最低分为486分，平均分为506分，最低位次号为183515。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了484分，高于省控线492分，低于最高分513分，对应的情况为大于等于省控线且小于最高分，小于等于最低分，选择情况，因此不能报考医学检验技术专业，对应的的情况为不可以报考医学检验技术专业。因此，我不能报考医学检验技术专业，对应的的情况为不可以报考医学检验技术专业。&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>{'detail': {'专业': '建筑学', '平均分': 546, '序号': 8, '录取数': 54, '最低位次号': 120613, '最低分': 542, '最高分': 572, '省控线': 492, '计划数': 54}, 'score': 600, 'rank': None}</t>
@@ -708,7 +708,7 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了600分，能否报考建筑学专业？&lt;REASONING&gt;好的，针对我考了600分，能否报考建筑学专业？的问题，可以搜索到如下相关信息浙江省2024年本科建筑学录取情况如下浙江省2024年本科建筑学专业的省控线为492分。最高分为572分，最低分为542分，平均分为546分，最低位次号为120613。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了600分，能够报考建筑学专业&lt;/SOLUTION&gt;</t>
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了600分，能否报考建筑学专业？&lt;REASONING&gt;好的，针对我考了600分，能否报考建筑学专业？的问题，可以搜索到如下相关信息浙江省2024年本科建筑学录取情况如下浙江省2024年本科建筑学专业的录取数为54人，省控线为492分。最高分为572分，最低分为542分，平均分为546分，最低位次号为120613。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了600分，能够报考建筑学专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了600分，能否报考建筑学专业？&lt;REASONING&gt;好的，针对我考了600分，能否报考建筑学专业？的问题，可以搜索到如下相关信息浙江省2024年本科建筑学录取情况如下浙江省2024年本科建筑学专业的录取数为54人，省控线为492分。最高分为572分，最低分为542分，平均分为546分，最低位次号为120613。&lt;/REASON&gt;&lt;SOLUTION&gt;我考了600分，能够报考建筑学专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="135" customHeight="1">
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我考了600分，能否报考建筑学专业？&lt;REASONING&gt;好的，针对“我考了600分，能否报考建筑学专业？”的问题，可以搜索到如下相关信息浙江省2024年本科建筑学专业的录取计划数为54人，录取数为54人，省控线为492分。最高分为572分，最低分为542分，平均分为546分，最低位次号为120613。&lt;/REASONING&gt;&lt;SOLUTION&gt;我考了600分，高于省控线492分，低于最高分554分，对应的情况为大于或等于省控线且小于最高分，选择情况，因此可以报考建筑学专业，对应的的情况为是大于或等于省控线且小于最高分，选择。因此，我考了600分，能够报考建筑学专业，对应的的情况为是是大于或等于省控线且小于最高分，选择。&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="165" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>{'detail': {'专业': '物联网工程', '平均分': 503, '序号': 29, '录取数': 51, '最低位次号': 172871, '最低分': 496, '最高分': 529, '省控线': 492, '计划数': 51}, 'score': None, 'rank': 134879}</t>
@@ -739,7 +739,7 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为134879，能否报考物联网工程专业？&lt;REASONING&gt;好的，针对我的位次为134879，能否报考物联网工程专业？的问题，可以搜索到如下相关信息浙江省2024年本科物联网工程录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['161214', '物联网工程', '51', '51', '492', '529', '496', '503', '172813']&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为134879，可以报考物联网工程专业&lt;/SOLUTION&gt;</t>
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为134879，能否报考物联网工程专业？&lt;REASONING&gt;好的，针对我的位次为134879，能否报考物联网工程专业？的问题，可以搜索到如下相关信息浙江省2024年本科物联网工程录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['161214', '物联网工程', '51', '51', '492', '529', '496', '503', '172881']&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为134879，可以报考物联网工程专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -747,11 +747,11 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为134879，能否报考物联网工程专业？&lt;REASONING&gt;好的，针对我的位次为134879，能否报考物联网工程专业？的问题，可以搜索到如下相关信息浙江省2024年本科物联网工程录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '物联网工程', '51', '51', '492', '529', '496', '503', '168841']&lt;/REASON&gt;&lt;SOLUTION&gt;我的位次为134879，可以报考物联网工程专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="135" customHeight="1">
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为134879，能否报考物联网工程专业？&lt;REASONING&gt;好的，针对“我的位次为134879，能否报考物联网工程专业？”的问题，可以搜索到如下相关信息浙江省2024年本科物联网工程专业的录取计划数为51人，录取数为51人，省控线为492分。最高分为529分，最低分为496分，平均分为503分，最低位次号为172871。&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为172871，高于省控线492分，低于最高分529分，对应的情况为大于等于492且小于519分，小于529分，选择情况，因此可以报考物联网工程专业，对应的的情况为是大于等于492且小于519分，小于529分，选择。因此，我的位次为172871，可以报考物联网工程专业，对应的的情况为是大于等于492且小于519分，小于529分，选择。&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>{'detail': {'专业': '家政学', '平均分': 555, '序号': 24, '录取数': 13, '最低位次号': 109812, '最低分': 551, '最高分': 563, '省控线': 492, '计划数': 13}, 'score': None, 'rank': 139298}</t>
@@ -770,7 +770,7 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为139298，能否报考家政学专业？&lt;REASONING&gt;好的，针对我的位次为139298，能否报考家政学专业？的问题，可以搜索到如下相关信息浙江省2024年本科家政学录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['161312', '家政学', '13人', '13人', '492分', '563分', '551分', '555分', '109812']&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为139298，可以报考家政学专业&lt;/SOLUTION&gt;</t>
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为139298，能否报考家政学专业？&lt;REASONING&gt;好的，针对我的位次为139298，能否报考家政学专业？的问题，可以搜索到如下相关信息浙江省2024年本科家政学录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['161213', '家政学', '13人', '13人', '492分', '563分', '551分', '555分', '109812']&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为139298，可以报考家政学专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -778,11 +778,11 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为139298，能否报考家政学专业？&lt;REASONING&gt;好的，针对我的位次为139298，能否报考家政学专业？的问题，可以搜索到如下相关信息浙江省2024年本科家政学录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '家政学录取情况', '13人', '13人', '492分', '563分', '551分', '555分', '109812']&lt;/REASON&gt;&lt;SOLUTION&gt;我的位次为139298，可以报考家政学专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="135" customHeight="1">
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为139298，能否报考家政学专业？&lt;REASONING&gt;好的，针对“我的位次为139298，能否报考家政学专业？”的问题，可以搜索到如下相关信息浙江省2024年本科家政学专业的录取计划数为13人，录取数为13人，省控线为492分。最高分为563分，最低分为551分，平均分为555分，最低位次号为109812。&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为139298，高于省控线492分，低于555分，对应的情况为大于等于492且小于556分，小于559分，选择情况，因此不能报考家政学专业，对应的的情况为不可以报考家政学专业。因此，我的位次为139298，不能报考家政学专业，对应的的情况为不可以报考家政学专业。&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>{'detail': {'专业': '环境工程', '平均分': 485, '序号': 31, '录取数': 100, '最低位次号': 193639, '最低分': 477, '最高分': 519, '省控线': 492, '计划数': 100}, 'score': None, 'rank': 103570}</t>
@@ -809,11 +809,11 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为103570，能否报考环境工程专业？&lt;REASONING&gt;好的，针对我的位次为103570，能否报考环境工程专业？的问题，可以搜索到如下相关信息浙江省2024年本科环境工程录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['103', '环境工程', '100', '100', '492', '519', '477', '485', '196639']&lt;/REASON&gt;&lt;SOLUTION&gt;我的位次为103570，可以报考环境工程专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="135" customHeight="1">
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为103570，能否报考环境工程专业？&lt;REASONING&gt;好的，针对“我的位次为103570，能否报考环境工程专业？”的问题，可以搜索到如下相关信息浙江省2024年本科环境工程专业的录取计划数为100人，录取数为100人，省控线为492分。最高分为519分，最低分为477分，平均分为485分，最低位次号为193639。&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为193639，高于省控线492分，低于最高分519分，对应的情况为大于等于省控线且小于最高分，选择情况，因此可以报考环境工程专业，对应的的情况为是是大于等于省控线且小于最高分，选择。因此，我的位次为193639，能够报考环境工程专业，对应的的情况为是是大于等于省控线且小于最高分，选择。&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="180" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>{'detail': {'专业': '城乡规划', '平均分': 549, '序号': 6, '录取数': 60, '最低位次号': 116183, '最低分': 546, '最高分': 559, '省控线': 492, '计划数': 60}, 'score': None, 'rank': 174322}</t>
@@ -840,11 +840,11 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为174322，能否报考城乡规划专业？&lt;REASONING&gt;好的，针对我的位次为174322，能否报考城乡规划专业？的问题，可以搜索到如下相关信息浙江省2024年本科城乡规划录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['163', '城乡规划', '60', '60', '492', '559', '546', '549', '174322']&lt;/REASON&gt;&lt;SOLUTION&gt;我的位次为174322，可以报考城乡规划专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="150" customHeight="1">
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为174322，能否报考城乡规划专业？&lt;REASONING&gt;好的，针对“我的位次为174322，能否报考城乡规划专业？”的问题，可以搜索到如下相关信息浙江省2024年本科城乡规划录取情况如下浙江省2024年本科城乡规划专业的录取计划数为60人，录取数为60人，省控线为492分。最高分为559分，最低分为546分，平均分为549分，最低位次号为116183。&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为174322，高于省控线492分，低于最高分555分，对应的情况为大于或等于省控线且小于最高分，小于最低位次号，因此不能报考城乡规划专业，对应的的情况为大于或等于省控线且小于最高分，小于最低位次号。因此，我的位次为174322，不能报考城乡规划专业，对应的的情况为不可以报考城乡规划专业。因此，我的位次为174322，不能报考城乡规划专业，对应的的情况为不可以报考城乡规划专业。&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="165" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>{'detail': {'专业': '公共事业管理', '平均分': 551, '序号': 5, '录取数': 20, '最低位次号': 112613, '最低分': 549, '最高分': 569, '省控线': 492, '计划数': 20}, 'score': None, 'rank': 176158}</t>
@@ -863,7 +863,7 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为176158，能否报考公共事业管理专业？&lt;REASONING&gt;好的，针对我的位次为176158，能否报考公共事业管理专业？的问题，可以搜索到如下相关信息浙江省2024年本科公共事业管理录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['193613', '公共事业管理', '20', '20', '492', '569', '549', '551', '176158']&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为176158，可以报考公共事业管理专业&lt;/SOLUTION&gt;</t>
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为176158，能否报考公共事业管理专业？&lt;REASONING&gt;好的，针对我的位次为176158，能否报考公共事业管理专业？的问题，可以搜索到如下相关信息[{'role': 'user', 'content': '我的位次为176158，能否报考公共事业管理专业？'}, {'role': 'assistant', 'content': '可以'}]&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为176158，能够报考公共事业管理专业&lt;/SOLUTION&gt;</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -871,7 +871,7 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为176158，能否报考公共事业管理专业？&lt;REASONING&gt;好的，针对我的位次为176158，能否报考公共事业管理专业？的问题，可以搜索到如下相关信息浙江省2024年本科公共事业管理录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['193', '公共事业管理', '20', '20', '492', '569', '549', '551', '176158']&lt;/REASON&gt;&lt;SOLUTION&gt;我的位次为176158，可以报考公共事业管理专业&lt;/SOLUTION&gt;</t>
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为176158，能否报考公共事业管理专业？&lt;REASONING&gt;好的，针对“我的位次为176158，能否报考公共事业管理专业？”的问题，可以搜索到如下相关信息浙江省2024年本科公共事业管理专业的录取计划数为20人，录取数为20人，省控线为492分。最高分为569分，最低分为549分，平均分为551分，最低位次号为112613。&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为176158，高于省控线492分，低于553分，对应的情况为大于或等于492且小于549分，小于551分，选择情况，因此不能报考公共事业管理专业，对应的的情况为不可以报考公共事业管理专业。因此，我的位次为176158，不能报考公共事业管理专业，对应的的情况为不可以报考公共事业管理专业。&lt;/SOLUTION&gt;</t>
         </is>
       </c>
     </row>
@@ -902,11 +902,11 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为122789，能否报考人工智能专业？&lt;REASONING&gt;好的，针对我的位次为122789，能否报考人工智能专业？的问题，可以搜索到如下相关信息浙江省2024年本科人工智能录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['191', '人工智能', '99', '99', '492', '524', '496', '503', '173398']&lt;/REASON&gt;&lt;SOLUTION&gt;我的位次为122789，可以报考人工智能专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="150" customHeight="1">
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为122789，能否报考人工智能专业？&lt;REASONING&gt;好的，针对“我的位次为122789，能否报考人工智能专业？”的问题，可以搜索到如下相关信息浙江省2024年本科人工智能专业的录取计划数为99人，录取数为99人，省控线为492分。最高分为524分，最低分为496分，平均分为503分，最低位次号为173398。&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为173398，高于省控线492分，低于最高分524分，对应的情况为大于等于496分且小于512分，小于524分，选择情况，因此可以报考人工智能专业，对应的的情况为大于等于496分且小于512分，小于524分，选择。我的位次号为173398。&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="165" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>{'detail': {'专业': '医学检验技术', '平均分': 506, '序号': 39, '录取数': 43, '最低位次号': 183515, '最低分': 486, '最高分': 541, '省控线': 492, '计划数': 43}, 'score': None, 'rank': 126367}</t>
@@ -933,11 +933,11 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为126367，能否报考医学检验技术专业？&lt;REASONING&gt;好的，针对我的位次为126367，能否报考医学检验技术专业？的问题，可以搜索到如下相关信息浙江省2024年本科医学检验技术录取情况如下。\n['序号', '专业', '计划数', '录取数', '省控线', '最高分', '最低分', '平均分', '最低位次号']\n['1', '医学检验技术', '43人', '43人', '492分', '541分', '486分', '506分', '183515']&lt;/REASON&gt;&lt;SOLUTION&gt;我的位次为126367，可以报考医学检验技术专业&lt;/SOLUTION&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="135" customHeight="1">
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为126367，能否报考医学检验技术专业？&lt;REASONING&gt;好的，针对“我的位次为126367，能否报考医学检验技术专业？”的问题，可以搜索到如下相关信息浙江省2024年本科医学检验技术专业的录取计划数为43人，录取数为43人，省控线为492分。最高分为541分，最低分为486分，平均分为506分，最低位次号为183515。&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为183515，高于省控线492分，低于最高分541分，对应的情况为大于等于485分且小于536分，小于541分，选择情况，因此可以报考医学检验技术专业，对应的的情况为是大于等于485分且小于536分，小于541分，选择。因此，我的位次为183515，可以报考医学检验技术专业，对应的的情况为是大于等于485分且小于536分，小于541分，选择。&lt;/SOLUTION&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>{'detail': {'专业': '建筑学', '平均分': 546, '序号': 8, '录取数': 54, '最低位次号': 120613, '最低分': 542, '最高分': 572, '省控线': 492, '计划数': 54}, 'score': None, 'rank': 187928}</t>
@@ -964,7 +964,7 @@
           <t>You are given a problem.
 Think about the problem and provide your working out.
 Place your reason between &lt;REASONING&gt; and &lt;/REASONING&gt;.
-Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为187928，能否报考建筑学专业？&lt;REASONING&gt;好的，针对我的位次为187928，能否报考建筑学专业？的问题，可以搜索到如下相关信息浙江省2024年本科建筑学录取情况如下浙江省2024年本科建筑学专业的录取数为54人，省控线为492分。最高分为572分，最低分为542分，平均分为546分，最低位次号为120613。&lt;/REASON&gt;&lt;SOLUTION&gt;我的位次为187928，不能报考建筑学专业&lt;/SOLUTION&gt;</t>
+Then, provide your solution between &lt;SOLUTION&gt;&lt;/SOLUTION&gt;我的位次为187928，能否报考建筑学专业？&lt;REASONING&gt;好的，针对“我的位次为187928，能否报考建筑学专业？”的问题，可以搜索到如下相关信息浙江省2024年本科建筑学专业的录取计划数为54人，录取数为54人，省控线为492分。最高分为572分，最低分为542分，平均分为546分，最低位次号为120613。&lt;/REASONING&gt;&lt;SOLUTION&gt;我的位次为187928，高于省控线492分，低于最高分554分，对应的情况为大于等于492且小于542分，小于555分，选择情况，因此不能报考建筑学专业，对应的的情况为不可以报考建筑学专业。因此，我的位次为187928，不能报考建筑学专业，对应的的情况为不可以报考建筑学专业。&lt;/SOLUTION&gt;</t>
         </is>
       </c>
     </row>
